--- a/quote_for_20_and_90_microscopes.xlsx
+++ b/quote_for_20_and_90_microscopes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.maia\Documents\GitHub\malaria-detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5544021C-D1EA-4226-9D01-73777330779D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA46300-0535-4B3E-8D10-EC73B4DF013F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7290" xr2:uid="{DAF13A40-EE2D-4B8F-8FAE-F4FBC27C5E25}"/>
   </bookViews>
@@ -78,9 +78,6 @@
     <t>torch</t>
   </si>
   <si>
-    <t>https://aliexpress.com/item/1005006344009961.html</t>
-  </si>
-  <si>
     <t>https://www.aliexpress.com/item/1005008613864647.html</t>
   </si>
   <si>
@@ -162,7 +159,10 @@
     <t>100X oil variant</t>
   </si>
   <si>
-    <t>variant with included batteries</t>
+    <t>https://www.aliexpress.com/item/1005007578277944.html</t>
+  </si>
+  <si>
+    <t>variant with included batteries &amp; charger</t>
   </si>
 </sst>
 </file>
@@ -554,13 +554,13 @@
         <v>1</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" t="s">
         <v>8</v>
@@ -569,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -593,7 +593,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I2">
         <v>420</v>
@@ -618,7 +618,7 @@
         <v>104.2</v>
       </c>
       <c r="P2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -635,7 +635,7 @@
         <v>1.5</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3">
         <v>26</v>
@@ -658,7 +658,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4">
         <v>362</v>
@@ -695,7 +695,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -704,10 +704,10 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6">
         <v>150</v>
@@ -730,10 +730,10 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I7">
         <v>80</v>
@@ -779,7 +779,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
         <v>45</v>
@@ -796,7 +796,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -805,10 +805,10 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I11">
         <v>60</v>
@@ -822,7 +822,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -831,10 +831,10 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
         <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
       </c>
       <c r="I12">
         <v>83</v>
@@ -848,7 +848,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -857,10 +857,10 @@
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13">
         <v>320</v>
@@ -874,7 +874,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -883,10 +883,10 @@
         <v>1.5</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I14">
         <v>22</v>
@@ -900,7 +900,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -909,10 +909,10 @@
         <v>0.1</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -935,10 +935,10 @@
         <v>0.25</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I16">
         <v>4.3899999999999997</v>
@@ -948,9 +948,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F9" r:id="rId1" xr:uid="{E6FD1A64-1BA2-4A9C-A982-B0220E55EDB1}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>